--- a/outputs/evaluation/requirement/design/v1/CF_M08/third/CF_M08_req_eval_by_type.xlsx
+++ b/outputs/evaluation/requirement/design/v1/CF_M08/third/CF_M08_req_eval_by_type.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,47 +457,39 @@
           <t>recall</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>qr</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.8571</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>qr</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -519,41 +511,35 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8571</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8571</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -584,11 +570,6 @@
       </c>
       <c r="H5" t="n">
         <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
   </sheetData>
